--- a/artfynd/A 6890-2021 artfynd.xlsx
+++ b/artfynd/A 6890-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117589808</v>
       </c>
       <c r="B2" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>117589777</v>
       </c>
       <c r="B3" t="n">
-        <v>90425</v>
+        <v>90427</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
